--- a/ip6-validasyon/etkinlik_bazli_etki.xlsx
+++ b/ip6-validasyon/etkinlik_bazli_etki.xlsx
@@ -468,47 +468,47 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>44.18</v>
+        <v>17.89</v>
       </c>
       <c r="D2" t="n">
         <v>4113</v>
       </c>
       <c r="E2" t="n">
-        <v>9.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>8.69</v>
       </c>
       <c r="G2" t="n">
-        <v>0.040815</v>
+        <v>0.323891</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>has_proje</t>
+          <t>has_lab</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>303</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>21.85</v>
+        <v>15.97</v>
       </c>
       <c r="D3" t="n">
-        <v>3830</v>
+        <v>3994</v>
       </c>
       <c r="E3" t="n">
-        <v>8.359999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="F3" t="n">
-        <v>13.49</v>
+        <v>6.96</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.000535</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -517,26 +517,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>has_lab</t>
+          <t>has_proje</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>303</v>
       </c>
       <c r="C4" t="n">
-        <v>19.96</v>
+        <v>15.54</v>
       </c>
       <c r="D4" t="n">
-        <v>3994</v>
+        <v>3830</v>
       </c>
       <c r="E4" t="n">
-        <v>8.98</v>
+        <v>8.75</v>
       </c>
       <c r="F4" t="n">
-        <v>10.98</v>
+        <v>6.79</v>
       </c>
       <c r="G4" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -545,26 +545,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>has_uygulama</t>
+          <t>has_sinav</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382</v>
+        <v>4039</v>
       </c>
       <c r="C5" t="n">
-        <v>16.57</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>3751</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>8.609999999999999</v>
+        <v>3.11</v>
       </c>
       <c r="F5" t="n">
-        <v>7.95</v>
+        <v>6.28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00017</v>
+        <v>0.002847</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -580,47 +580,47 @@
         <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>15.83</v>
+        <v>13.59</v>
       </c>
       <c r="D6" t="n">
         <v>3821</v>
       </c>
       <c r="E6" t="n">
-        <v>8.82</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>7.01</v>
+        <v>4.7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.017526</v>
+        <v>0.081982</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>has_sinav</t>
+          <t>has_uygulama</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4039</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>9.5</v>
+        <v>12.37</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>3751</v>
       </c>
       <c r="E7" t="n">
-        <v>3.02</v>
+        <v>8.93</v>
       </c>
       <c r="F7" t="n">
-        <v>6.47</v>
+        <v>3.44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00505</v>
+        <v>5.4e-05</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -636,19 +636,19 @@
         <v>723</v>
       </c>
       <c r="C8" t="n">
-        <v>12.83</v>
+        <v>11.28</v>
       </c>
       <c r="D8" t="n">
         <v>3410</v>
       </c>
       <c r="E8" t="n">
-        <v>8.609999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="F8" t="n">
-        <v>4.22</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00236</v>
+        <v>0.041852</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
